--- a/public/static/供应商价格导入模板.xlsx
+++ b/public/static/供应商价格导入模板.xlsx
@@ -33,6 +33,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>供应商编码(</t>
     </r>
     <r>
@@ -58,6 +65,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>品名规格(</t>
     </r>
     <r>
@@ -83,6 +97,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>协议价(含税)(</t>
     </r>
     <r>
@@ -108,6 +129,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>税率</t>
     </r>
     <r>
@@ -122,7 +150,7 @@
     </r>
   </si>
   <si>
-    <t>协议价（不含税）</t>
+    <t>协议价(不含税)</t>
   </si>
   <si>
     <r>
